--- a/if and nested Example.xlsx
+++ b/if and nested Example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Desktop\ifrah\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSI\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B554490-4A3F-4FA7-B8AC-C66B9A92F357}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15383BB9-848A-4107-A2E7-060FE64F3050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Students" sheetId="1" r:id="rId1"/>
@@ -1225,58 +1225,6 @@
   </cellStyles>
   <dxfs count="50">
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -1512,6 +1460,19 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -1724,6 +1685,19 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1859,7 +1833,30 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2113,6 +2110,9 @@
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2127,22 +2127,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9B93B7D1-B605-4E7F-9283-6DF17AA95F85}" name="Table1" displayName="Table1" ref="A1:J61" totalsRowShown="0" headerRowDxfId="2" dataDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9B93B7D1-B605-4E7F-9283-6DF17AA95F85}" name="Table1" displayName="Table1" ref="A1:J61" totalsRowShown="0" headerRowDxfId="49" dataDxfId="48">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{EDB29417-F5CF-4623-A96C-668FFE21CC5C}" name="RollNo" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{54BA50FE-24CC-4ED7-92F0-DC7A7CB543C0}" name="Name" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{8C6DF1DD-C750-48A4-B41E-DCABEAD1C82F}" name="Gender" dataDxfId="46"/>
-    <tableColumn id="4" xr3:uid="{F9363144-C961-4701-BC19-F233CD2168A1}" name="Class" dataDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{164D3765-23EA-4CB5-B85A-269125797456}" name="Marks1" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{B73C6D70-EC8F-4042-999D-9627A0AE2065}" name="Marks2" dataDxfId="43"/>
-    <tableColumn id="7" xr3:uid="{0F5FB85C-56C0-4AFB-933F-C4E7A0799FCB}" name="Marks3" dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{1419A308-D9E2-40DB-8413-3B6371993D52}" name="Total" dataDxfId="41">
+    <tableColumn id="1" xr3:uid="{EDB29417-F5CF-4623-A96C-668FFE21CC5C}" name="RollNo" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{54BA50FE-24CC-4ED7-92F0-DC7A7CB543C0}" name="Name" dataDxfId="46"/>
+    <tableColumn id="3" xr3:uid="{8C6DF1DD-C750-48A4-B41E-DCABEAD1C82F}" name="Gender" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{F9363144-C961-4701-BC19-F233CD2168A1}" name="Class" dataDxfId="44"/>
+    <tableColumn id="5" xr3:uid="{164D3765-23EA-4CB5-B85A-269125797456}" name="Marks1" dataDxfId="43"/>
+    <tableColumn id="6" xr3:uid="{B73C6D70-EC8F-4042-999D-9627A0AE2065}" name="Marks2" dataDxfId="42"/>
+    <tableColumn id="7" xr3:uid="{0F5FB85C-56C0-4AFB-933F-C4E7A0799FCB}" name="Marks3" dataDxfId="41"/>
+    <tableColumn id="8" xr3:uid="{1419A308-D9E2-40DB-8413-3B6371993D52}" name="Total" dataDxfId="40">
       <calculatedColumnFormula>SUM(E2:G2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{58EB3398-F146-462C-A09D-1245A2307149}" name="Result" dataDxfId="40">
+    <tableColumn id="9" xr3:uid="{58EB3398-F146-462C-A09D-1245A2307149}" name="Result" dataDxfId="39">
       <calculatedColumnFormula>IF(OR(E2&lt;35, F2&lt;35, G2&lt;35),"Fail","Pass")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{DDA6BFC6-D230-4542-9875-8BF789428312}" name="Grade" dataDxfId="39">
+    <tableColumn id="10" xr3:uid="{DDA6BFC6-D230-4542-9875-8BF789428312}" name="Grade" dataDxfId="38">
       <calculatedColumnFormula>IF(H2/3&gt;75, "A",IF(H2/3&gt;65, "B", IF(H2/3&gt;50, "C", "D")))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2151,15 +2151,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3EA257C3-C1AA-41F6-9C48-768F3A774E82}" name="Table2" displayName="Table2" ref="A1:G61" totalsRowShown="0" headerRowDxfId="1" dataDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3EA257C3-C1AA-41F6-9C48-768F3A774E82}" name="Table2" displayName="Table2" ref="A1:G61" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{30346F1E-B700-4AB8-841F-36230A06B5CD}" name="SKU" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{95E1F671-2AFF-491B-AC66-BBCA94F693C7}" name="Product" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{C1DBC621-9889-4D97-A831-DEB25FCA5F0D}" name="Category" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{07D9CFB2-1E9A-48A4-834F-2B233E943EAB}" name="Supplier" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{03A42A6F-7F69-4817-8B66-C2B0E3F4A407}" name="Quantity" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{61D92478-D9FB-465F-81AC-42EBD46A3CE3}" name="Order Qty" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{FA7917CC-0137-4F3E-95CF-36A1ECF14710}" name="Status" dataDxfId="30">
+    <tableColumn id="1" xr3:uid="{30346F1E-B700-4AB8-841F-36230A06B5CD}" name="SKU" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{95E1F671-2AFF-491B-AC66-BBCA94F693C7}" name="Product" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{C1DBC621-9889-4D97-A831-DEB25FCA5F0D}" name="Category" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{07D9CFB2-1E9A-48A4-834F-2B233E943EAB}" name="Supplier" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{03A42A6F-7F69-4817-8B66-C2B0E3F4A407}" name="Quantity" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{61D92478-D9FB-465F-81AC-42EBD46A3CE3}" name="Order Qty" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{FA7917CC-0137-4F3E-95CF-36A1ECF14710}" name="Status" dataDxfId="27">
       <calculatedColumnFormula>IF(E2-F2, E2-F2, F2-E2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2168,18 +2168,18 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5E5A72E1-98FC-46FB-A883-E57E2CB7ACA6}" name="Table3" displayName="Table3" ref="A1:H61" totalsRowShown="0" headerRowDxfId="3" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27" totalsRowBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5E5A72E1-98FC-46FB-A883-E57E2CB7ACA6}" name="Table3" displayName="Table3" ref="A1:H61" totalsRowShown="0" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23" totalsRowBorderDxfId="22">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{E3E0C0F5-41ED-4882-997F-50670AE029B9}" name="EmpID" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{ECC30205-C00D-4612-84F9-F02896B16A51}" name="Name" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{2953F787-A71A-41A8-9CCD-911AF82FB101}" name="Dept" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{EDA0DE8B-ABE3-42A3-A64A-5AE2F5554483}" name="Salary" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{758B1331-F224-450A-B199-096B82E407DB}" name="Experience" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{FFDC6343-F335-473C-AFE8-59BEA283F32D}" name="Rating" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{E62A3685-3297-43A7-8791-9DCF824791C6}" name="Status" dataDxfId="19">
+    <tableColumn id="1" xr3:uid="{E3E0C0F5-41ED-4882-997F-50670AE029B9}" name="EmpID" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{ECC30205-C00D-4612-84F9-F02896B16A51}" name="Name" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{2953F787-A71A-41A8-9CCD-911AF82FB101}" name="Dept" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{EDA0DE8B-ABE3-42A3-A64A-5AE2F5554483}" name="Salary" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{758B1331-F224-450A-B199-096B82E407DB}" name="Experience" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{FFDC6343-F335-473C-AFE8-59BEA283F32D}" name="Rating" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{E62A3685-3297-43A7-8791-9DCF824791C6}" name="Status" dataDxfId="15">
       <calculatedColumnFormula>IF(AND(E2&gt;=8,F2&gt;=4),"Promote", "Hold on")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{38E2F439-36B9-4EAD-A551-D1E87C2DB0C7}" name="Bonus" dataDxfId="18">
+    <tableColumn id="8" xr3:uid="{38E2F439-36B9-4EAD-A551-D1E87C2DB0C7}" name="Bonus" dataDxfId="14">
       <calculatedColumnFormula>IF(AND(E2&gt;=10,F2=5), 15%, IF(AND(E2&gt;=8, F2=4), 10%, IF(AND(E2&gt;=6, F2=3), 5%, 2%)))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2188,21 +2188,21 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{059FFAED-8F61-4276-A3B1-AEAB7215341E}" name="Table4" displayName="Table4" ref="A1:I61" totalsRowShown="0" headerRowDxfId="4" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{059FFAED-8F61-4276-A3B1-AEAB7215341E}" name="Table4" displayName="Table4" ref="A1:I61" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10" totalsRowBorderDxfId="9">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{D626A8F5-3EDF-479F-9F04-069CB49C165E}" name="Invoice" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{81733407-5C34-4387-8B14-CA98F25BCFD2}" name="Salesman" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{194E9DAA-5F9A-44C2-BB0D-D96D3FB7F918}" name="Region" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{17D17D68-049E-4CB5-83B8-37018330C6B4}" name="Month" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{7010038E-959B-4469-BFE8-69FE67FF1271}" name="Units" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{F14BE004-6C90-4E18-B41A-85995952090E}" name="UnitPrice" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{B0CDD236-2B1D-48E8-B8D5-CED320BC2ACE}" name="Revenue" dataDxfId="7">
+    <tableColumn id="1" xr3:uid="{D626A8F5-3EDF-479F-9F04-069CB49C165E}" name="Invoice" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{81733407-5C34-4387-8B14-CA98F25BCFD2}" name="Salesman" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{194E9DAA-5F9A-44C2-BB0D-D96D3FB7F918}" name="Region" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{17D17D68-049E-4CB5-83B8-37018330C6B4}" name="Month" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{7010038E-959B-4469-BFE8-69FE67FF1271}" name="Units" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{F14BE004-6C90-4E18-B41A-85995952090E}" name="UnitPrice" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{B0CDD236-2B1D-48E8-B8D5-CED320BC2ACE}" name="Revenue" dataDxfId="2">
       <calculatedColumnFormula>E2*F2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{284A81F8-6B7E-4064-BD82-716A24769D54}" name="Discount" dataDxfId="6">
+    <tableColumn id="8" xr3:uid="{284A81F8-6B7E-4064-BD82-716A24769D54}" name="Discount" dataDxfId="1">
       <calculatedColumnFormula>IF(G2&gt;100000, 20%, IF(G2&gt;75000, 15%, IF(G2&gt;50000, 10%, IF(G2&gt;25000, 5%, 2%))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3C8B494F-FFA4-4DA1-9F79-BD470A92E51A}" name="Discount with amount" dataDxfId="5">
+    <tableColumn id="9" xr3:uid="{3C8B494F-FFA4-4DA1-9F79-BD470A92E51A}" name="Discount with amount" dataDxfId="0">
       <calculatedColumnFormula>IF(G2&gt;100000,G2-G2*20%,IF(G2&gt;75000,G2-G2*15%,IF(G2&gt;50000,G2-G2*10%,IF(G2&gt;25000,G2-G2*5%,G2-G2*2%))))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6127,10 +6127,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="cellIs" dxfId="38" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="37" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
